--- a/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
@@ -48,12 +48,12 @@
     <t xml:space="preserve">Freirina</t>
   </si>
   <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Caldera</t>
   </si>
   <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>129</v>
+        <v>138.56</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>106.16</v>
+        <v>113.87</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>99.07</v>
+        <v>106.65</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>96.56</v>
+        <v>103.43</v>
       </c>
     </row>
     <row r="6">
@@ -567,13 +567,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3102</v>
+        <v>3201</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>94.47</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="7">
@@ -584,13 +584,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3201</v>
+        <v>3102</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>94.33</v>
+        <v>101.53</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>78.87</v>
+        <v>84.76</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>68.53</v>
+        <v>73.32</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>65.38</v>
+        <v>70.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:02</t>
+    <t xml:space="preserve">2026-10-05 16:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
